--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -443,14 +443,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
           <t>Examples</t>
@@ -458,24 +458,24 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Comment</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BCIO:026003</t>
+          <t>BFO:0000029</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>attribute of location</t>
+          <t>site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -484,25 +484,30 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Features of a given location, such as social and economic characteristics.</t>
+          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BFO_0000029</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCIO:026007</t>
+          <t>BCIO:026046</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>population and resource density</t>
+          <t>outdoor environment</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -510,7 +515,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
+          <t>A site which is an outdoor location outside of a building.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -522,99 +527,114 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BCIO:050914</t>
+          <t>ENVO:00000111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>urban area</t>
+          <t>forest area</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
+          <t>An area with a high density of trees. A small forest may be called a wood</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ENVO:00000111</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIO:026008</t>
+          <t>ENVO:00000064</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>suburban area</t>
+          <t>road</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
+          <t>An open way for the passage of vehicles, persons, or animals on land</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ENVO:00000064</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:050915</t>
+          <t>ENVO:00000562</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rural area</t>
+          <t>park</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ENVO:00000562</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:026004</t>
+          <t>ENVO:00000106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>area social and economic condition</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>grassland area</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -622,123 +642,108 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>disadvantaged area; crime rates; World Bank Classifications</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ENVO:00000106</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:026005</t>
+          <t>BCIO:026047</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>low-income area</t>
+          <t>water</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
+          <t>An outdoor environment set in an expanse of water.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">developing country </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:026006</t>
+          <t>BCIO:026048</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>high-income area</t>
+          <t>path or pavement</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
+          <t>An outdoor environment for the passage of persons or cyclists on land</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>developed country</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BFO:0000029</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
+          <t>BCIO:026050</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>path or pavement for cyclists</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A three-dimensional immaterial entity that is (partially or wholly) bounded by a material entity or it is a three-dimensional immaterial part thereof.</t>
+          <t>A path or pavement for the passage of people using bicycles only on land.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>BFO_0000029</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:026046</t>
+          <t>BCIO:026049</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>outdoor environment</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>path or pavement for pedestrians</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A site which is an outdoor location outside of a building.</t>
+          <t>A path or pavement for the passage of persons only on land.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -750,156 +755,171 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:026048</t>
+          <t>ENVO:00000091</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>path or pavement</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>An outdoor environment for the passage of persons or cyclists on land</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ENVO:00000091</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:026050</t>
+          <t>BCIO:026041</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>transportation</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>path or pavement for cyclists</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of people using bicycles only on land.</t>
+          <t>Methods of traveling from one place to another.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NCIT_C141286</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:026049</t>
+          <t>BCIO:026043</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>path or pavement for pedestrians</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>private transportation</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A path or pavement for the passage of persons only on land.</t>
+          <t>A form of transportation owned by an individual for individual or group use.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>car; bicycle; motorbike</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:026047</t>
+          <t>BCIO:026044</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>mobile intervention venue</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>An outdoor environment set in an expanse of water.</t>
+          <t>A form of transportation delivering interventions in transient locations.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>mobile van</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENVO:00000562</t>
+          <t>BCIO:026045</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation</t>
+          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ENVO:00000562</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENVO:00000106</t>
+          <t>BCIO:026042</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>grassland area</t>
+          <t>public transportation</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
+          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -907,216 +927,196 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ENVO:00000106</t>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NCIT:C141287</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>bus; train; plane</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENVO:00000064</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>BCIO:026003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>attribute of location</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>road</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land</t>
+          <t>Features of a given location, such as social and economic characteristics.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ENVO:00000064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENVO:00000091</t>
+          <t>BCIO:026007</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>beach</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>population and resource density</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
+          <t>An attribute of location describing the density of an area, in terms of people and resources within it.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ENVO:00000091</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENVO:00000111</t>
+          <t>BCIO:050915</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>forest area</t>
+          <t>rural area</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
+          <t>A population and resource density that involves being outside of an urban or suburban area and has a low density of population and buildings.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ENVO:00000111</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:026041</t>
+          <t>BCIO:026008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>suburban area</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Methods of traveling from one place to another.</t>
+          <t>A population and resource density that involves being on the edge of a large town or city where a proportion of those who work in the town or city live.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NCIT_C141286</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:026042</t>
+          <t>BCIO:050914</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>public transportation</t>
+          <t>urban area</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Forms of transportation that run on fixed routes and are available to the public, usually for a set fare</t>
+          <t>A population and resource density that involves a high density of human population and of a built environment consisting of structures and infrastructure designed to support human habitation.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>NCIT:C141287</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>bus; train; plane</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:026045</t>
+          <t>BCIO:026004</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ambulance</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>area social and economic condition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A form of transporation which can transport patients for health treatment, and in some instances will also provide out-of-hospital healthcare to the patient.</t>
+          <t>An attribute of location describing the overall socioeconomic state of a location.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>disadvantaged area; crime rates; World Bank Classifications</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:026044</t>
+          <t>BCIO:026005</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>mobile intervention venue</t>
+          <t>low-income area</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A form of transportation delivering interventions in transient locations.</t>
+          <t>An area social and economic condition described to have a low-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1126,28 +1126,28 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>mobile van</t>
+          <t xml:space="preserve">developing country </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:026043</t>
+          <t>BCIO:026006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>private transportation</t>
+          <t>high-income area</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A form of transportation owned by an individual for individual or group use.</t>
+          <t>An area social and economic condition described to have a high-income, whether at a country or within-country level.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>car; bicycle; motorbike</t>
+          <t>developed country</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>GAZ:00000448</t>
         </is>
@@ -1305,7 +1305,7 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>OMRSE:00000062</t>
         </is>
@@ -1314,47 +1314,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:026039</t>
+          <t>BCIO:026040</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>factory facility</t>
+          <t>military facility</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
+          <t>A facility relating to or characteristic of soldiers or armed forces</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>army; navy; air force</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:026029</t>
+          <t>BCIO:026036</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>community facility</t>
+          <t>retail facility</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
+          <t>A facility used as an outlet for shopping.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1364,28 +1369,28 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>food bank; recycling centre</t>
+          <t>supermarket; market; shopping centre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:026033</t>
+          <t>BCIO:026029</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>religious facility</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>community facility</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
+          <t>A facility used by a group of people living in the same place or having a particular characteristic in common.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1395,14 +1400,14 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>mosque; church; temple</t>
+          <t>food bank; recycling centre</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:026032</t>
+          <t>BCIO:026034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1410,25 +1415,30 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>library facility</t>
+          <t>hospitality and catering facility</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A community facility containing a collection of books and learning resources for loan.</t>
+          <t>A community facility used to serve food.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>diner; restaurant; pub; bar</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:026035</t>
+          <t>BCIO:026031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1436,13 +1446,13 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>arts and entertainment facility</t>
+          <t>social centre or Community Hall facility</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A community facility designed to entertain or amuse.</t>
+          <t>A community facility used for socialising by those living in a given area.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1452,7 +1462,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>cinema; theatre; disco</t>
+          <t>YMCA; working mens club</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1500,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:026031</t>
+          <t>BCIO:026035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1498,13 +1508,13 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>social centre or Community Hall facility</t>
+          <t>arts and entertainment facility</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A community facility used for socialising by those living in a given area.</t>
+          <t>A community facility designed to entertain or amuse.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1514,14 +1524,14 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>YMCA; working mens club</t>
+          <t>cinema; theatre; disco</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:026034</t>
+          <t>BCIO:026032</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1529,70 +1539,70 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>hospitality and catering facility</t>
+          <t>library facility</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A community facility used to serve food.</t>
+          <t>A community facility containing a collection of books and learning resources for loan.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>diner; restaurant; pub; bar</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:026037</t>
+          <t>BCIO:026033</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>office facility</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>religious facility</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
+          <t>A community facility where individuals or a group of people come to perform acts of devotion and veneration.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>mosque; church; temple</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMRSE:00000102</t>
+          <t>ENVO:00000469</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>health care facility</t>
+          <t>research facility</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
+          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1600,30 +1610,35 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>OMRSE:00000102</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ENVO:00000469</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>research lab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PDRO:0000074</t>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>pharmacy facility</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>residential facility</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
+          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1631,16 +1646,16 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>PDRO:0000074</t>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>OMRSE:00000191</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:026051</t>
+          <t>BCIO:026010</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1648,13 +1663,13 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>psychiatric facility</t>
+          <t>multiple occupancy residence</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
+          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1662,56 +1677,61 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>NCIT:C53536</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>bedsit</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:026021</t>
+          <t>BCIO:026012</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>dentist facility</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>residential care or assisted living</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A healthcare facility where dental healthcare is provided.</t>
+          <t>A multiple occupancy residence where multiple vulnerable people live</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>retirement home</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OMRSE:00000106</t>
+          <t>BCIO:026011</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>rehabilitation facility</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>student residence</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A facility to assist in physical or addiction recovery</t>
+          <t>A multiple occupancy residence where many students live.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1719,30 +1739,30 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>OMRSE:00000106</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>student hall</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:026018</t>
+          <t>BCIO:026009</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>drug or alcohol rehabilitation facility</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>household residence</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
+          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1754,7 +1774,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:026016</t>
+          <t>BCIO:026014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1762,13 +1782,13 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>doctor-led primary care facility</t>
+          <t>temporary residence</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>A healthcare facility led by doctors.</t>
+          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1778,14 +1798,14 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>general practitioners surgery; doctor surgery</t>
+          <t>Hostels; BandB; emergency accomnodation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:026019</t>
+          <t>BCIO:026013</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1793,13 +1813,13 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>community healthcare facility</t>
+          <t>homeless setting</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>A clinic providing healthcare services to people in a certain area</t>
+          <t>A residential facility where an individual is living that is not stable and secure.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1809,40 +1829,45 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>polyclinic</t>
+          <t xml:space="preserve">an architectural structure for which an individual does not have a legal right to stay </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:026020</t>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>health care facility</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>community outpatient clinic facility</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
+          <t>A facility that’s administered by a health care organisation for the purpose of providing health care to a patient population</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>OMRSE:00000102</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OMRSE:00000063</t>
+          <t>BCIO:026019</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1850,13 +1875,13 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>hospital facility</t>
+          <t>community healthcare facility</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
+          <t>A clinic providing healthcare services to people in a certain area</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1864,16 +1889,16 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>OMRSE:00000063</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>polyclinic</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:026015</t>
+          <t>BCIO:026020</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1882,12 +1907,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>hospital outpatient clinic facility</t>
+          <t>community outpatient clinic facility</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
+          <t>A healthcare facility to treat patients in the community without them staying overnight.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -1899,28 +1924,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OMRSE:00000114</t>
+          <t>BCIO:026017</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>emergency department facility</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>care home facility</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
+          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:026017</t>
+          <t>BCIO:026051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1928,25 +1958,30 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>care home facility</t>
+          <t>psychiatric facility</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A healthcare facility that is run by a care home organization and is the bearer of a care home function.</t>
+          <t>A place designed and staffed to house and treat individuals that need assistance with mental dysfunctions</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NCIT:C53536</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OMRSE:00000104</t>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1954,13 +1989,13 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>hospice facility</t>
+          <t>rehabilitation facility</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
+          <t>A facility to assist in physical or addiction recovery</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -1968,47 +2003,42 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>OMRSE:00000104</t>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>OMRSE:00000106</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OMRSE:00000191</t>
+          <t>BCIO:026018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>residential facility</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>drug or alcohol rehabilitation facility</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A facility that has at least one housing unit as part in which a person or persons live</t>
+          <t>A rehabilitation facility to assist the recovery of people with drug or alcohol addiction.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>OMRSE:00000191</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:026014</t>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2016,13 +2046,13 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>temporary residence</t>
+          <t>hospital facility</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A residential facility where individuals are in a transitional state of housing and not staying for a prolonged period.</t>
+          <t>A facility that is run by a hospital organization, such as emergency departments, outpatient clinics and rehabilitation and is the bearer of a hospital function</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2030,30 +2060,30 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Hostels; BandB; emergency accomnodation</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>OMRSE:00000063</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:026009</t>
+          <t>BCIO:026015</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>household residence</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>hospital outpatient clinic facility</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A facility where an individual is living alone or with one or more person. The individuals do not have to be related.</t>
+          <t>A hospital facility to treat patients without them staying overnight, often after a hospital visit.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2065,52 +2095,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:026010</t>
+          <t>OMRSE:00000114</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>multiple occupancy residence</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>emergency department facility</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>A facility where an individual lives with many others that may be collected according to a social structure such as education or disability.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>bedsit</t>
+          <t>A health care facility that bears a function to provide emergency healthcare services and the acute care of patients who present without prior appointment, having arrived either by their own means or by ambulance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:026011</t>
+          <t>PDRO:0000074</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>student residence</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>pharmacy facility</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where many students live.</t>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2118,30 +2138,30 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>student hall</t>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PDRO:0000074</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:026012</t>
+          <t>BCIO:026016</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>residential care or assisted living</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>doctor-led primary care facility</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A multiple occupancy residence where multiple vulnerable people live</t>
+          <t>A healthcare facility led by doctors.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2151,14 +2171,14 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>retirement home</t>
+          <t>general practitioners surgery; doctor surgery</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:026013</t>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2166,13 +2186,13 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>homeless setting</t>
+          <t>hospice facility</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A residential facility where an individual is living that is not stable and secure.</t>
+          <t>A health care facility that bears a function to provide healthcare to the sick or terminally ill</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2180,61 +2200,56 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an architectural structure for which an individual does not have a legal right to stay </t>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>OMRSE:00000104</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:026040</t>
+          <t>BCIO:026021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>military facility</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>dentist facility</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A facility relating to or characteristic of soldiers or armed forces</t>
+          <t>A healthcare facility where dental healthcare is provided.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>army; navy; air force</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:026022</t>
+          <t>BCIO:026039</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>educational facility</t>
+          <t>factory facility</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A facility in which formal education is provided to a student population.</t>
+          <t>A facility of a building or group of buildings where goods are manufactured or assembled chiefly by machine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2246,64 +2261,64 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:026027</t>
+          <t>BCIO:026038</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>vocational facility</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>criminal justice facility</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
+          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>prison</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:026023</t>
+          <t>BCIO:026022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>early years facility</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>educational facility</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>An educational facility in which pre-school education is provided.</t>
+          <t>A facility in which formal education is provided to a student population.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nursery school </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:026028</t>
+          <t>BCIO:026023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2311,25 +2326,30 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>university facility</t>
+          <t>early years facility</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>An educational facility in which students study for degrees and academic research is done.</t>
+          <t>An educational facility in which pre-school education is provided.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Setting</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nursery school </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OMRSE:00000064</t>
+          <t>BCIO:026028</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2337,34 +2357,39 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>school facility</t>
+          <t>university facility</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function</t>
+          <t>An educational facility in which students study for degrees and academic research is done.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Setting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:026024</t>
+          <t>BCIO:026027</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>primary school</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>vocational facility</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A school facility for younger children, typically aged between five and eleven.</t>
+          <t>An educational facility providing practically based, occupationally-specific teaching.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2376,33 +2401,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:026025</t>
+          <t>OMRSE:00000064</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>middle school</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>school facility</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>A school facility providing education between primary and secondary school.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Setting</t>
+          <t>A facility that is run by a school organization and is the bearer of a school function</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:026026</t>
+          <t>BCIO:026024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2411,74 +2431,64 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>secondary school</t>
+          <t>primary school</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
+          <t>A school facility for younger children, typically aged between five and eleven.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>high school</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:026036</t>
+          <t>BCIO:026025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>retail facility</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>middle school</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A facility used as an outlet for shopping.</t>
+          <t>A school facility providing education between primary and secondary school.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>supermarket; market; shopping centre</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENVO:00000469</t>
+          <t>BCIO:026026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>research facility</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>secondary school</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>A facility, permanent or temporary, on land, in air, space or water, where scientific research or measurements can be undertaken</t>
+          <t>A school facility for older children and teenagers, typically aged between eleven and eighteen.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2486,45 +2496,35 @@
           <t>Setting</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>ENVO:00000469</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>research lab</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:026038</t>
+          <t>BCIO:026037</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>criminal justice facility</t>
+          <t>office facility</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>A facility where individuals are being reprimanded, detained or imprisoned.</t>
+          <t>A facility of a room, set of rooms, or building used as a place for commercial, professional, or bureaucratic work.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Setting</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>prison</t>
         </is>
       </c>
     </row>

--- a/Setting/BCIO-setting-hierarchy.xlsx
+++ b/Setting/BCIO-setting-hierarchy.xlsx
@@ -517,7 +517,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>dose range specification</t>
+          <t>spécification d’intervalle de dose</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A bodily disposition that is realized in a mental process.</t>
+          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -3012,7 +3012,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -3047,7 +3047,7 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
+          <t>An open way for the passage of vehicles, persons, or animals on land</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -3112,7 +3112,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -3542,7 +3542,7 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -3602,7 +3602,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -3687,7 +3687,7 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation</t>
+          <t>A bounded area of land, or water, usually in its natural or semi-natural (landscaped) state and set aside for some purpose, usually to do with recreation or conservation.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of wate</t>
+          <t>A landform consisting of loose rock particles such as sand, gravel, shingle, pebbles, cobble, or even shell fragments along the shoreline of a body of water.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -3952,7 +3952,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>An area in which grasses (Graminae) are a significant component of the vegetation.</t>
+          <t>An area in which grasses (Graminae) are a significant component of the vegetation</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>An area with a high density of trees. A small forest may be called a wood</t>
+          <t>An area with a high density of trees. A small forest may be called a wood.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -4147,7 +4147,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>An open way for the passage of vehicles, persons, or animals on land.</t>
+          <t>An open way for the passage of vehicles, persons, or animals on land</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -4942,7 +4942,7 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -5602,7 +5602,7 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>A facility that is run by a school organization and is the bearer of a school function</t>
+          <t>A facility that is run by a school organization and is the bearer of a school function.</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>An affective process that involves the experience of internal or external sensory stimuli.</t>
+          <t>The subjective emotional feeling is that (fiat) part of the emotion process by which the organism experiences its own emotion.</t>
         </is>
       </c>
     </row>
